--- a/cfg/excel/CollectionCfg.xlsx
+++ b/cfg/excel/CollectionCfg.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="31230" windowHeight="15135"/>
+    <workbookView windowWidth="19200" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="146">
   <si>
     <t>##var</t>
   </si>
@@ -57,6 +57,9 @@
     <t>characterId</t>
   </si>
   <si>
+    <t>collectionIcon</t>
+  </si>
+  <si>
     <t>collectionTime</t>
   </si>
   <si>
@@ -69,33 +72,6 @@
     <t>tipsTween</t>
   </si>
   <si>
-    <t>useWays</t>
-  </si>
-  <si>
-    <t>rarity</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>maxCount</t>
-  </si>
-  <si>
-    <t>overlayMaxCount</t>
-  </si>
-  <si>
-    <t>storageType</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>sellingPrice</t>
-  </si>
-  <si>
-    <t>usedInBackpack</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -114,12 +90,6 @@
     <t>CollectionBase</t>
   </si>
   <si>
-    <t>(list#sep=,),UseWay</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -135,6 +105,9 @@
     <t>角色表</t>
   </si>
   <si>
+    <t>收集物icon</t>
+  </si>
+  <si>
     <t>收集时间</t>
   </si>
   <si>
@@ -147,106 +120,361 @@
     <t>提示词飘字</t>
   </si>
   <si>
-    <t>使用方法</t>
-  </si>
-  <si>
-    <t>稀有度</t>
-  </si>
-  <si>
-    <t>道具类型</t>
-  </si>
-  <si>
-    <t>储存最大个数</t>
-  </si>
-  <si>
-    <t>叠加最多个数</t>
-  </si>
-  <si>
-    <t>用于区分道具存放哪个页签</t>
-  </si>
-  <si>
-    <t>购买价格</t>
-  </si>
-  <si>
-    <t>出售价格</t>
-  </si>
-  <si>
-    <t>可以在背包使用</t>
-  </si>
-  <si>
     <t>给玩家加弹药</t>
   </si>
   <si>
+    <t>弹药包</t>
+  </si>
+  <si>
+    <t>Ammo</t>
+  </si>
+  <si>
+    <t>Collection_Ammo1</t>
+  </si>
+  <si>
+    <t>LBulletCollection_30</t>
+  </si>
+  <si>
+    <t>小弹药</t>
+  </si>
+  <si>
+    <t>+30弹药</t>
+  </si>
+  <si>
+    <t>MBulletCollection_60</t>
+  </si>
+  <si>
+    <t>中弹药</t>
+  </si>
+  <si>
+    <t>+60弹药</t>
+  </si>
+  <si>
+    <t>HBulletCollection_90</t>
+  </si>
+  <si>
+    <t>大弹药</t>
+  </si>
+  <si>
+    <t>+90弹药</t>
+  </si>
+  <si>
+    <t>给玩家加护甲</t>
+  </si>
+  <si>
+    <t>护甲</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>Collection_Armor1</t>
+  </si>
+  <si>
+    <t>ArmorCollection_50</t>
+  </si>
+  <si>
+    <t>+50护甲</t>
+  </si>
+  <si>
+    <t>给玩家加血包</t>
+  </si>
+  <si>
+    <t>血包</t>
+  </si>
+  <si>
+    <t>Cure</t>
+  </si>
+  <si>
+    <t>Collection_Cure1</t>
+  </si>
+  <si>
+    <t>CureCollection_30_2</t>
+  </si>
+  <si>
+    <t>+30血包</t>
+  </si>
+  <si>
+    <t>给玩家加防弹衣</t>
+  </si>
+  <si>
+    <t>防弹衣1</t>
+  </si>
+  <si>
+    <t>BodyArmor</t>
+  </si>
+  <si>
+    <t>Collection_BodyArmor1</t>
+  </si>
+  <si>
+    <t>LBodyArmorCollection_1</t>
+  </si>
+  <si>
+    <t>防弹衣</t>
+  </si>
+  <si>
+    <t>+1级防弹衣</t>
+  </si>
+  <si>
+    <t>防弹衣2</t>
+  </si>
+  <si>
+    <t>Collection_BodyArmor2</t>
+  </si>
+  <si>
+    <t>MBodyArmorCollection_2</t>
+  </si>
+  <si>
+    <t>+2级防弹衣</t>
+  </si>
+  <si>
+    <t>防弹衣3</t>
+  </si>
+  <si>
+    <t>Collection_BodyArmor3</t>
+  </si>
+  <si>
+    <t>HBodyArmorCollection_3</t>
+  </si>
+  <si>
+    <t>+3级防弹衣</t>
+  </si>
+  <si>
+    <t>给玩家加穿透等级</t>
+  </si>
+  <si>
+    <t>穿甲弹1</t>
+  </si>
+  <si>
+    <t>Grip</t>
+  </si>
+  <si>
+    <t>Collection_Grip1</t>
+  </si>
+  <si>
+    <t>LGripCollection_1</t>
+  </si>
+  <si>
+    <t>穿甲弹</t>
+  </si>
+  <si>
+    <t>+1级穿透等级</t>
+  </si>
+  <si>
+    <t>穿甲弹2</t>
+  </si>
+  <si>
+    <t>Collection_Grip2</t>
+  </si>
+  <si>
+    <t>MGripCollection_2</t>
+  </si>
+  <si>
+    <t>+2级穿透等级</t>
+  </si>
+  <si>
+    <t>穿甲弹3</t>
+  </si>
+  <si>
+    <t>Collection_Grip3</t>
+  </si>
+  <si>
+    <t>HGripCollection_3</t>
+  </si>
+  <si>
+    <t>+3级穿透等级</t>
+  </si>
+  <si>
+    <t>使玩家的瞄准更快</t>
+  </si>
+  <si>
+    <t>握把1</t>
+  </si>
+  <si>
+    <t>Handle</t>
+  </si>
+  <si>
+    <t>Collection_Handle1</t>
+  </si>
+  <si>
+    <t>LHandleCollection_1</t>
+  </si>
+  <si>
+    <t>握把</t>
+  </si>
+  <si>
+    <t>-15%子弹散布</t>
+  </si>
+  <si>
+    <t>使玩家的瞄准更快，散步更低</t>
+  </si>
+  <si>
+    <t>握把2</t>
+  </si>
+  <si>
+    <t>Collection_Handle2</t>
+  </si>
+  <si>
+    <t>MHandleCollection_2</t>
+  </si>
+  <si>
+    <t>-20%子弹散布，-20%瞄准时间</t>
+  </si>
+  <si>
+    <t>握把3</t>
+  </si>
+  <si>
+    <t>Collection_Handle3</t>
+  </si>
+  <si>
+    <t>HHandleCollection_3</t>
+  </si>
+  <si>
+    <t>-30%子弹散布，-40%瞄准时间</t>
+  </si>
+  <si>
+    <t>使玩家弹夹容量扩大</t>
+  </si>
+  <si>
     <t>弹夹</t>
   </si>
   <si>
-    <t>Ammo</t>
-  </si>
-  <si>
-    <t>BulletCollection_60</t>
-  </si>
-  <si>
-    <t>弹药</t>
-  </si>
-  <si>
-    <t>+60弹药</t>
-  </si>
-  <si>
-    <t>给玩家加护甲</t>
-  </si>
-  <si>
-    <t>护甲</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>ArmorCollection_50</t>
-  </si>
-  <si>
-    <t>+50护甲</t>
-  </si>
-  <si>
-    <t>给玩家加血包</t>
-  </si>
-  <si>
-    <t>血包</t>
-  </si>
-  <si>
-    <t>Cure</t>
-  </si>
-  <si>
-    <t>CureCollection_30_2</t>
-  </si>
-  <si>
-    <t>+30血包</t>
-  </si>
-  <si>
-    <t>给玩家加防弹衣</t>
-  </si>
-  <si>
-    <t>防弹衣</t>
-  </si>
-  <si>
-    <t>BodyArmor</t>
-  </si>
-  <si>
-    <t>BodyArmorCollection_1</t>
-  </si>
-  <si>
-    <t>+1级防弹衣</t>
-  </si>
-  <si>
-    <t>BodyArmorCollection_2</t>
-  </si>
-  <si>
-    <t>+2级防弹衣</t>
-  </si>
-  <si>
-    <t>BodyArmorCollection_3</t>
-  </si>
-  <si>
-    <t>+3级防弹衣</t>
+    <t>Magazine</t>
+  </si>
+  <si>
+    <t>Collection_Magazine1</t>
+  </si>
+  <si>
+    <t>LMagazineCollection_1</t>
+  </si>
+  <si>
+    <t>+20%装弹速度</t>
+  </si>
+  <si>
+    <t>使玩家的拾音范围扩大</t>
+  </si>
+  <si>
+    <t>战术雷达1</t>
+  </si>
+  <si>
+    <t>Radar</t>
+  </si>
+  <si>
+    <t>Collection_Radar1</t>
+  </si>
+  <si>
+    <t>LRadarCollection_1</t>
+  </si>
+  <si>
+    <t>战术雷达</t>
+  </si>
+  <si>
+    <t>+10%拾音范围</t>
+  </si>
+  <si>
+    <t>战术雷达2</t>
+  </si>
+  <si>
+    <t>Collection_Radar2</t>
+  </si>
+  <si>
+    <t>MRadarCollection_2</t>
+  </si>
+  <si>
+    <t>+20%拾音范围</t>
+  </si>
+  <si>
+    <t>战术雷达3</t>
+  </si>
+  <si>
+    <t>Collection_Radar3</t>
+  </si>
+  <si>
+    <t>HRadarCollection_3</t>
+  </si>
+  <si>
+    <t>+30%拾音范围</t>
+  </si>
+  <si>
+    <t>使玩家视野和射击距离提升</t>
+  </si>
+  <si>
+    <t>瞄准镜</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Collection_Scope1</t>
+  </si>
+  <si>
+    <t>LScopeCollection_1</t>
+  </si>
+  <si>
+    <t>+10%视野范围</t>
+  </si>
+  <si>
+    <t>使玩家移速提升，移动响度降低</t>
+  </si>
+  <si>
+    <t>战术靴1</t>
+  </si>
+  <si>
+    <t>Shoe</t>
+  </si>
+  <si>
+    <t>Collection_Shoe1</t>
+  </si>
+  <si>
+    <t>LShoeCollection_1</t>
+  </si>
+  <si>
+    <t>战术靴</t>
+  </si>
+  <si>
+    <t>-10%移动响度</t>
+  </si>
+  <si>
+    <t>战术靴2</t>
+  </si>
+  <si>
+    <t>Collection_Shoe2</t>
+  </si>
+  <si>
+    <t>MShoeCollection_2</t>
+  </si>
+  <si>
+    <t>-15%移动响度，+5%移动速度</t>
+  </si>
+  <si>
+    <t>战术靴3</t>
+  </si>
+  <si>
+    <t>Collection_Shoe3</t>
+  </si>
+  <si>
+    <t>HShoeCollection_3</t>
+  </si>
+  <si>
+    <t>-25%移动响度，+10%移动速度</t>
+  </si>
+  <si>
+    <t>降低射击响度，提升子弹射速</t>
+  </si>
+  <si>
+    <t>消音器</t>
+  </si>
+  <si>
+    <t>Silencer</t>
+  </si>
+  <si>
+    <t>Collection_Silencer1</t>
+  </si>
+  <si>
+    <t>LSilencerCollection_1</t>
+  </si>
+  <si>
+    <t>-20%射击响度</t>
   </si>
 </sst>
 </file>
@@ -929,7 +1157,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -963,8 +1191,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1277,32 +1511,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.3833333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="35.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="23.875" style="3" customWidth="1"/>
     <col min="6" max="6" width="16.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="21.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="37.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="18" style="3" customWidth="1"/>
-    <col min="11" max="11" width="29" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.1333333333333" style="3" customWidth="1"/>
-    <col min="13" max="13" width="13.875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="16.125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="22.375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="30.5" style="3" customWidth="1"/>
-    <col min="17" max="17" width="13.8833333333333" style="3" customWidth="1"/>
-    <col min="18" max="18" width="18.8833333333333" style="3" customWidth="1"/>
-    <col min="19" max="19" width="21.25" style="3" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="3"/>
+    <col min="7" max="7" width="37.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="37.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="35.125" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1336,390 +1562,920 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:11">
+      <c r="A3" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:19">
-      <c r="A3" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:19">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:11">
       <c r="A4" s="6"/>
       <c r="B4" s="7">
         <v>1001</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F4" s="7">
         <v>1006</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="9">
         <v>2</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>48</v>
-      </c>
       <c r="I4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:19">
+        <v>31</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:11">
       <c r="A5" s="6"/>
       <c r="B5" s="7">
         <v>1002</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F5" s="7">
-        <v>1007</v>
-      </c>
-      <c r="G5" s="9">
+        <v>1006</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="9">
         <v>2</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="I5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:19">
+        <v>34</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:11">
       <c r="A6" s="6"/>
       <c r="B6" s="7">
         <v>1003</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F6" s="7">
-        <v>1008</v>
-      </c>
-      <c r="G6" s="9">
+        <v>1006</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="9">
         <v>2</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="I6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:19">
+        <v>37</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:11">
       <c r="A7" s="6"/>
       <c r="B7" s="7">
         <v>1004</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F7" s="7">
-        <v>1009</v>
-      </c>
-      <c r="G7" s="9">
+        <v>1006</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="9">
         <v>2</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="I7" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:19">
+        <v>44</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:11">
       <c r="A8" s="6"/>
       <c r="B8" s="7">
         <v>1005</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F8" s="7">
-        <v>1009</v>
-      </c>
-      <c r="G8" s="9">
+        <v>1006</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="9">
         <v>2</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>66</v>
-      </c>
       <c r="I8" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:19">
+        <v>50</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:11">
       <c r="A9" s="6"/>
       <c r="B9" s="7">
         <v>1006</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="9">
+        <v>2</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:11">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7">
+        <v>1007</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="9">
+        <v>2</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="J10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="7" t="s">
+    </row>
+    <row r="11" customHeight="1" spans="1:11">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7">
+        <v>1008</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="7">
+      <c r="E11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="9">
+        <v>2</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:11">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7">
         <v>1009</v>
       </c>
-      <c r="G9" s="9">
+      <c r="C12" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="11">
         <v>2</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="I12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:11">
+      <c r="B13" s="7">
+        <v>1010</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:19">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
+      <c r="F13" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="11">
+        <v>2</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:11">
+      <c r="B14" s="7">
+        <v>1011</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="11">
+        <v>1006</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="11">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:11">
+      <c r="B15" s="7">
+        <v>1012</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="11">
+        <v>2</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:11">
+      <c r="B16" s="7">
+        <v>1013</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="11">
+        <v>1006</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="11">
+        <v>2</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:11">
+      <c r="B17" s="7">
+        <v>1014</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="11">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:11">
+      <c r="B18" s="7">
+        <v>1015</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="11">
+        <v>1006</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" s="11">
+        <v>2</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:11">
+      <c r="B19" s="7">
+        <v>1016</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="11">
+        <v>2</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:11">
+      <c r="B20" s="7">
+        <v>1017</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="11">
+        <v>1006</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="11">
+        <v>2</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:11">
+      <c r="B21" s="7">
+        <v>1018</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" s="11">
+        <v>2</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:11">
+      <c r="B22" s="7">
+        <v>1019</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="11">
+        <v>1006</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="11">
+        <v>2</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:11">
+      <c r="B23" s="7">
+        <v>1020</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="11">
+        <v>2</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:11">
+      <c r="B24" s="7">
+        <v>1021</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="11">
+        <v>1006</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24" s="11">
+        <v>2</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:11">
+      <c r="B25" s="7">
+        <v>1022</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H25" s="11">
+        <v>2</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="2:11">
+      <c r="B26" s="7">
+        <v>1023</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F26" s="11">
+        <v>1006</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H26" s="11">
+        <v>2</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:11">
+      <c r="B27" s="11"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" customHeight="1" spans="2:11">
+      <c r="B28" s="11"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" customHeight="1" spans="2:11">
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="11"/>
+    </row>
+    <row r="30" customHeight="1" spans="2:11">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="11"/>
+    </row>
+    <row r="31" customHeight="1" spans="2:11">
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="11"/>
+    </row>
+    <row r="32" customHeight="1" spans="2:11">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="11"/>
+    </row>
+    <row r="33" customHeight="1" spans="2:8">
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="11"/>
+    </row>
+    <row r="34" customHeight="1" spans="2:8">
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="11"/>
+    </row>
+    <row r="35" customHeight="1" spans="2:8">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="11"/>
+    </row>
+    <row r="36" customHeight="1" spans="2:8">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="11"/>
+    </row>
+    <row r="37" customHeight="1" spans="2:8">
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
